--- a/mistral_translate_work/split_by_prompt/excel/system_text/lang_hot_patch/lang_hot_patch__system_text__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/system_text/lang_hot_patch/lang_hot_patch__system_text__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Connecting</t>
+          <t>Đang kết nối</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Downloading: {0} Tốc độ: {1} Dung lượng: {2}/{3}</t>
+          <t>Đang tải: {0} Tốc độ: {1} Dung lượng: {2}/{3}</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Bạn có thể thu nhỏ cửa sổ game trong khi tải xuống</t>
+          <t>Bạn có thể thu nhỏ cửa sổ trò chơi trong khi tải xuống</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Installing Update Resources</t>
+          <t>Đang cài đặt tài nguyên cập nhật</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Vui lòng không đóng game trong quá trình cài đặt</t>
+          <t>Vui lòng không đóng trò chơi trong quá trình cài đặt</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Verifying files integrity: {0}%</t>
+          <t>Đang xác minh tính toàn vẹn tệp: {0}%</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Failed to get update details</t>
+          <t>Không thể lấy chi tiết cập nhật</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Exit</t>
+          <t>Thoát</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Thử Lại</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Cập nhật hoàn tất. Vui lòng khởi động lại game.</t>
+          <t>Đã vá xong. Vui lòng khởi động lại trò chơi.</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Repair hoàn tất. Vui lòng khởi động lại game.</t>
+          <t>Sửa chữa hoàn tất. Vui lòng khởi động lại trò chơi.</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Vui lòng cho phép truy cập bộ nhớ trong Settings &gt; Ứng dụng và khởi động lại game để lưu tài nguyên cập nhật.</t>
+          <t>Vui lòng cho phép truy cập bộ nhớ trong Cài đặt &gt; Ứng dụng và khởi động lại trò chơi để lưu tài nguyên cập nhật.</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Insufficient storage space cho tài nguyên cập nhật {0}. Vui lòng xóa bớt tệp để giải phóng dung lượng và nhấn "Tiếp tục" để tiến hành tải xuống.</t>
+          <t>Không đủ dung lượng lưu trữ cho tài nguyên cập nhật {0}. Vui lòng xóa bớt tệp để giải phóng không gian và nhấn "Tiếp tục" để tiến hành tải xuống.</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Photosensitive Seizure Warning</t>
+          <t>Cảnh Báo Co Giật Do Nhạy Cảm Ánh Sáng</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Khi tiếp xúc với một số kích thích hình ảnh hoặc ánh sáng nhấp nháy, một tỷ lệ rất nhỏ người chơi (bao gồm những người bị động kinh và một số trường hợp chưa được chẩn đoán) có thể gặp phải cơn co giật, với các triệu chứng như chóng mặt, thay đổi sắc mặt, co giật mắt hoặc mặt, sùi bọt mép, mất phương hướng hoặc bất tỉnh, hoặc co thắt cơ không kiểm soát. Nếu bạn, gia đình hoặc người sống cùng gặp các triệu chứng tương tự, vui lòng tham khảo ý kiến bác sĩ trước khi chơi game. Nếu bạn gặp bất kỳ triệu chứng nào kể trên trong khi chơi, hãy dừng chơi ngay lập tức, tìm kiếm sự trợ giúp y tế càng sớm càng tốt và làm theo lời khuyên của bác sĩ.</t>
+          <t>Khi tiếp xúc với một số kích thích hình ảnh hoặc ánh sáng nhấp nháy, một tỷ lệ rất nhỏ người chơi (bao gồm cả những người bị động kinh và một số trường hợp chưa được chẩn đoán) có thể bị co giật, với các triệu chứng như chóng mặt, mặt tái nhợt, co giật mắt hoặc mặt, sùi bọt mép, mất phương hướng hoặc bất tỉnh, hoặc co thắt cơ không kiểm soát. Nếu bạn, gia đình hoặc người thân có các triệu chứng tương tự, vui lòng tham khảo ý kiến bác sĩ trước khi chơi game. Nếu bạn gặp bất kỳ triệu chứng nào kể trên trong khi chơi, hãy dừng chơi ngay lập tức, tìm kiếm sự trợ giúp y tế càng sớm càng tốt và làm theo lời khuyên của bác sĩ.</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Game loading...</t>
+          <t>Đang tải trò chơi...</t>
         </is>
       </c>
     </row>
@@ -2074,8 +2074,8 @@
         <is>
           <t>Nói không với nội dung game không phù hợp hoặc game lậu.
 Bảo vệ thông tin cá nhân để tránh lừa đảo.
-Play game có trách nhiệm để có trải nghiệm an toàn và vui vẻ.
-Sắp xếp thời gian hợp lý để có lối sống lành mạnh.</t>
+Chơi game có trách nhiệm để có trải nghiệm an toàn và vui vẻ.
+Sắp xếp thời gian hợp lý để duy trì lối sống lành mạnh.</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Giấy phép &amp; ISBN: 国新出审〔2023〕1802号 ISBN 978-7-498-12761-7 Nhà xuất bản: 成都盈众九州网络科技有限公司 Bản quyền: 广州库洛科技有限公司</t>
+          <t>Giấy phép &amp; ISBN: Quốc Tân Xuất Thẩm [2023] 1802号 ISBN 978-7-498-12761-7 Nhà xuất bản: Thành Đô Doanh Chúng Cửu Châu Mạng Lưới Khoa Học Kỹ Thuật Hữu Hạn Công Ty Bản quyền: Quảng Châu Khố Lạc Khoa Học Kỹ Thuật Hữu Hạn Công Ty</t>
         </is>
       </c>
     </row>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Áp dụng Cấu Hình Từ Xa thất bại. Vui lòng kiểm tra kết nối mạng và khởi động lại game.</t>
+          <t>Không thể áp dụng Cấu Hình Từ Xa. Vui lòng kiểm tra kết nối mạng và khởi động lại trò chơi.</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Initializing Hotfix...</t>
+          <t>Đang khởi tạo bản sửa lỗi nhanh...</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Applying Remote Configuration...</t>
+          <t>Áp dụng cấu hình từ xa...</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Failed to apply Remote Configuration</t>
+          <t>Không thể áp dụng Cấu Hình Từ Xa</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Checking for app updates...</t>
+          <t>Đang kiểm tra cập nhật ứng dụng...</t>
         </is>
       </c>
     </row>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Checking {0} version...</t>
+          <t>Đang kiểm tra phiên bản {0}...</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2595,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Analyzing tài nguyên bản vá...</t>
+          <t>Đang phân tích tài nguyên bản vá...</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Applying resource patches...</t>
+          <t>Đang áp dụng bản vá tài nguyên...</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Patching Complete</t>
+          <t>Đã vá xong</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Lấy danh sách bản vá thất bại: {0}</t>
+          <t>Không thể lấy danh sách bản vá: {0}</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Tải xuống tài nguyên bản vá thất bại: {0}</t>
+          <t>Không thể tải xuống tài nguyên bản vá: {0}</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Tải xuống tài nguyên bản vá thất bại: {0}</t>
+          <t>Không thể tải xuống tài nguyên bản vá: {0}</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Failed to load patch type</t>
+          <t>Không thể tải loại bản vá</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Phân tích danh sách bản vá thất bại. Vui lòng khởi động lại ứng dụng game và thử lại hoặc liên hệ bộ phận chăm sóc khách hàng.</t>
+          <t>Không thể phân tích danh sách bản vá. Vui lòng khởi động lại trò chơi và thử lại hoặc liên hệ bộ phận hỗ trợ khách hàng.</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Xác minh tính toàn vẹn file thất bại. Vui lòng khởi động lại game client và thử lại hoặc liên hệ bộ phận hỗ trợ khách hàng.</t>
+          <t>Không thể xác minh tính toàn vẹn của tệp. Vui lòng khởi động lại trò chơi và thử lại hoặc liên hệ bộ phận hỗ trợ khách hàng.</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Unknown Error</t>
+          <t>Lỗi không xác định</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Network Error</t>
+          <t>Lỗi Mạng</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3310,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>File Rename Error</t>
+          <t>Lỗi Đổi Tên Tệp</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Integrity verification failed</t>
+          <t>Xác minh toàn vẹn thất bại</t>
         </is>
       </c>
     </row>
@@ -3440,7 +3440,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Failed to store files</t>
+          <t>Lưu tệp thất bại</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Insufficient Storage Space</t>
+          <t>Không đủ dung lượng lưu trữ</t>
         </is>
       </c>
     </row>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Download Canceled</t>
+          <t>Đã Hủy Tải Xuống</t>
         </is>
       </c>
     </row>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Download Success</t>
+          <t>Tải xuống thành công</t>
         </is>
       </c>
     </row>
@@ -3700,7 +3700,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Compiling Shader: {0}</t>
+          <t>Đang biên dịch Shader: {0}</t>
         </is>
       </c>
     </row>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Áp dụng Cấu Hình Từ Xa thất bại. Vui lòng kiểm tra kết nối mạng và khởi động lại game.</t>
+          <t>Không thể áp dụng Cấu Hình Từ Xa. Vui lòng kiểm tra kết nối mạng và khởi động lại trò chơi.</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Details cập nhật</t>
+          <t>Chi tiết cập nhật</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4025,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Sẽ tải xuống {0} tài nguyên cho bản cập nhật. Tiếp tục?</t>
+          <t>Sẽ tải xuống {0} tài nguyên để cập nhật. Tiếp tục?</t>
         </is>
       </c>
     </row>
@@ -4090,7 +4090,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Tải Resources</t>
+          <t>Tải Xuống Tài Nguyên</t>
         </is>
       </c>
     </row>
@@ -4155,7 +4155,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Downloading: {0}/{1}</t>
+          <t>Đang tải: {0}/{1}</t>
         </is>
       </c>
     </row>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Download Speed: {0}</t>
+          <t>Tốc Độ Tải: {0}</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Phiên bản trình điều khiển điện thoại của bạn đã lỗi thời (phiên bản GL driver &lt; 378). Điều này có thể gây ra sự cố game trong quá trình chơi. Để đảm bảo trải nghiệm chơi game mượt mà, bạn nên cập nhật phiên bản hệ thống hoặc trình điều khiển GL.</t>
+          <t>Phiên bản trình điều khiển đồ họa trên điện thoại của bạn đã lỗi thời (phiên bản GL &lt; 378). Điều này có thể khiến trò chơi bị treo trong quá trình chơi. Để đảm bảo trải nghiệm mượt mà, bạn nên cập nhật phiên bản hệ thống hoặc trình điều khiển GL.</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Nhấn vào vùng trống để tiếp tục</t>
+          <t>Chạm vào vùng trống để tiếp tục</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Tài nguyên bản vá cục bộ sẽ bị xóa và tải lại. Bạn có muốn tiếp tục không?</t>
+          <t>Tài nguyên bản vá cục bộ sẽ bị xóa và tải lại. Bạn có muốn tiếp tục?</t>
         </is>
       </c>
     </row>
@@ -4545,7 +4545,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Clear Bản Vá</t>
+          <t>Mảnh Thanh Tẩy</t>
         </is>
       </c>
     </row>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Repair</t>
+          <t>Sửa chữa</t>
         </is>
       </c>
     </row>
@@ -4675,7 +4675,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Thiết bị của bạn đang sử dụng phiên bản vi xử lý cũ. Rất có thể bạn sẽ gặp tình trạng game bị crash. Vui lòng cân nhắc chuyển sang thiết bị khác để có trải nghiệm chơi game tốt hơn.</t>
+          <t>Thiết bị của bạn đang sử dụng bộ xử lý phiên bản cũ. Rất có thể trò chơi sẽ bị treo. Hãy cân nhắc đổi sang thiết bị khác để có trải nghiệm tốt hơn.</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Điều khoản Sử dụng</t>
+          <t>Điều Khoản Sử Dụng</t>
         </is>
       </c>
     </row>
@@ -4805,7 +4805,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Chính sách Bảo mật</t>
+          <t>Chính Sách Bảo Mật</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4870,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Children's Privacy Policy</t>
+          <t>Chính Sách Bảo Mật Dành Cho Trẻ Em</t>
         </is>
       </c>
     </row>
@@ -4936,8 +4936,8 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Để đảm bảo trải nghiệm chơi game, bạn sắp liên kết tài khoản PlayStation™Network với tài khoản Kuro Games.
-Bạn có thể hủy liên kết tài khoản thông qua trang web chính thức hoặc dịch vụ khách hàng của chúng tôi.</t>
+          <t>Để đảm bảo trải nghiệm chơi game của bạn, bạn sắp liên kết tài khoản PlayStation™Network với tài khoản Kuro Games.
+Bạn có thể hủy liên kết tài khoản thông qua trang web chính thức hoặc dịch vụ chăm sóc khách hàng của chúng tôi.</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Thông báo về Điều Khoản Sử Dụng và Privacy Policy</t>
+          <t>Thông báo về Điều khoản Sử dụng và Chính sách Bảo mật</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Trình điều khiển thiết bị của bạn đã lỗi thời, có thể gây ra tình trạng game bị crash thường xuyên. Để có trải nghiệm tốt hơn, vui lòng cân nhắc nâng cấp thiết bị.</t>
+          <t>Trình điều khiển thiết bị của bạn đã lỗi thời, có thể gây ra tình trạng trò chơi bị treo thường xuyên. Để có trải nghiệm tốt hơn, hãy cân nhắc nâng cấp thiết bị.</t>
         </is>
       </c>
     </row>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Khởi động game thất bại. Vui lòng kiểm tra trạng thái tài khoản PlayStation™ Network.</t>
+          <t>Không thể khởi động trò chơi. Vui lòng kiểm tra trạng thái tài khoản PlayStation™ Network của bạn.</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Đã có bản cập nhật game. Vui lòng thoát game để áp dụng bản cập nhật.</t>
+          <t>Bản cập nhật trò chơi đã có sẵn. Vui lòng thoát game để tiến hành cập nhật.</t>
         </is>
       </c>
     </row>
@@ -5392,7 +5392,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Test mạng</t>
+          <t>Kiểm Tra Mạng</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Proxy Test</t>
+          <t>Bài Kiểm Tra Ủy Quyền</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>DNS Resolution</t>
+          <t>Phân Giải DNS</t>
         </is>
       </c>
     </row>
@@ -5587,7 +5587,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Test Ping</t>
+          <t>Kiểm Tra Ping</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Test truy cập Web</t>
+          <t>Kiểm Tra Truy Cập Mạng</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>UDP Connectivity Test</t>
+          <t>Kiểm tra kết nối UDP</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Bắt đầu Test</t>
+          <t>Bắt Đầu Kiểm Tra</t>
         </is>
       </c>
     </row>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Testing…</t>
+          <t>Đang kiểm tra…</t>
         </is>
       </c>
     </row>
@@ -5977,7 +5977,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Đang test mạng. Nhấn lại để dừng test và thoát trang này.</t>
+          <t>Đang kiểm tra mạng. Nhấn lại để dừng kiểm tra và thoát khỏi trang này.</t>
         </is>
       </c>
     </row>
@@ -6107,7 +6107,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>DNS resolution error. Error code:</t>
+          <t>Lỗi phân giải DNS. Mã lỗi:</t>
         </is>
       </c>
     </row>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Ping Results:</t>
+          <t>Kết Quả Ping:</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Web access error. Error code:</t>
+          <t>Lỗi truy cập mạng. Mã lỗi:</t>
         </is>
       </c>
     </row>
@@ -6367,7 +6367,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Nhấn nút để bắt đầu test mạng.</t>
+          <t>Nhấn nút để bắt đầu kiểm tra mạng.</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Trace ID:</t>
+          <t>ID Theo Dõi:</t>
         </is>
       </c>
     </row>
@@ -6562,7 +6562,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Chọn máy chủ</t>
+          <t>Chọn Máy Chủ</t>
         </is>
       </c>
     </row>
@@ -6757,7 +6757,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Patching progress {0}%</t>
+          <t>Tiến trình vá: {0}%</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Failed to move file.</t>
+          <t>Không thể di chuyển tệp.</t>
         </is>
       </c>
     </row>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Upload Dữ liệu</t>
+          <t>Tải dữ liệu lên</t>
         </is>
       </c>
     </row>
@@ -7017,7 +7017,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Press {0} to continue</t>
+          <t>Nhấn {0} để tiếp tục</t>
         </is>
       </c>
     </row>
@@ -7147,7 +7147,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Storage space available: {0}</t>
+          <t>Dung lượng lưu trữ khả dụng: {0}</t>
         </is>
       </c>
     </row>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Storage space required: {0}</t>
+          <t>Dung lượng lưu trữ cần thiết: {0}</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Tải Resources Basic</t>
+          <t>Tải Xuống Tài Nguyên Cơ Bản</t>
         </is>
       </c>
     </row>
@@ -7342,7 +7342,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Basic Resources</t>
+          <t>Tài Nguyên Cơ Bản</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Basic Resources chỉ bao gồm các tài nguyên cần thiết để khởi động game. Các tài nguyên còn lại có thể được tải xuống trong nền khi bạn chơi game.</t>
+          <t>Tài Nguyên Cơ Bản chỉ bao gồm các tài nguyên cần thiết để khởi động trò chơi. Các tài nguyên còn lại có thể được tải nền trong khi bạn chơi.</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Tải Resources Full Đủ</t>
+          <t>Tải Xuống Toàn Bộ Tài Nguyên</t>
         </is>
       </c>
     </row>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Full Resources</t>
+          <t>Tài Nguyên Đầy Đủ</t>
         </is>
       </c>
     </row>
@@ -7602,7 +7602,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Tải toàn bộ tài nguyên game để trải nghiệm đầy đủ trò chơi.</t>
+          <t>Tải tất cả tài nguyên trò chơi để trải nghiệm đầy đủ.</t>
         </is>
       </c>
     </row>
@@ -7667,7 +7667,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Tải Resources</t>
+          <t>Tải Xuống Tài Nguyên</t>
         </is>
       </c>
     </row>
@@ -7732,7 +7732,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Download</t>
+          <t>Tải Xuống</t>
         </is>
       </c>
     </row>
@@ -7797,7 +7797,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Không Đủ Không Gian Lưu Trữ</t>
+          <t>Không đủ dung lượng lưu trữ</t>
         </is>
       </c>
     </row>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Insufficient storage space. Vui lòng giải phóng dung lượng và thử lại.</t>
+          <t>Không đủ dung lượng lưu trữ. Hãy giải phóng không gian và thử lại.</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Thử Lại</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Phát hiện không đủ dung lượng lưu trữ. Dung lượng trống cần thiết cho tải xuống gia tăng và xử lý: {0}. Vui lòng giải phóng đủ dung lượng để tiếp tục Download gia tăng hoặc chọn Download đầy đủ dựa trên dung lượng hiện có.
+          <t>Phát hiện không đủ dung lượng lưu trữ. Dung lượng trống cần thiết để tải xuống gia tăng và xử lý: {0}. Vui lòng giải phóng đủ không gian để tiếp tục Tải Xuống Gia Tăng hoặc chọn Tải Xuống Đầy Đủ dựa trên dung lượng khả dụng hiện tại.
 Kích thước gói gia tăng: {1}
 Kích thước gói đầy đủ: {2}</t>
         </is>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Incremental Download</t>
+          <t>Tải Xuống Gia Tăng</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8191,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Full Download</t>
+          <t>Tải Xuống Hoàn Tất</t>
         </is>
       </c>
     </row>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Đã vá xong. Game đang khởi động lại.</t>
+          <t>Đã vá xong. Trò chơi đang khởi động lại.</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Repair hoàn tất. Game đang khởi động lại.</t>
+          <t>Sửa chữa hoàn tất. Trò chơi đang khởi động lại.</t>
         </is>
       </c>
     </row>
@@ -8386,7 +8386,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Thoát</t>
+          <t>Rời đi</t>
         </is>
       </c>
     </row>
@@ -8451,7 +8451,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Switch Account</t>
+          <t>Đổi Tài Khoản</t>
         </is>
       </c>
     </row>
@@ -8516,7 +8516,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Đăng Nhập</t>
+          <t>Đăng nhập</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Tải dữ liệu nâng cấp thất bại. Vui lòng thử lại hoặc tải xuống đầy đủ.</t>
+          <t>Tải dữ liệu nâng cấp thất bại. Vui lòng thử lại hoặc tải toàn bộ dữ liệu.</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Full Download</t>
+          <t>Tải Xuống Hoàn Tất</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Thử Lại</t>
         </is>
       </c>
     </row>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Route Detection</t>
+          <t>Phát Hiện Lộ Trình</t>
         </is>
       </c>
     </row>
@@ -8841,7 +8841,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Storyline Resources</t>
+          <t>Tài Nguyên Cốt Truyện</t>
         </is>
       </c>
     </row>
@@ -8906,7 +8906,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Environment Resources</t>
+          <t>Tài Nguyên Môi Trường</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Storyline Resources</t>
+          <t>Tài Nguyên Cốt Truyện</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Environment Resources</t>
+          <t>Tài Nguyên Môi Trường</t>
         </is>
       </c>
     </row>
@@ -9101,7 +9101,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Tài nguyên cốt truyện trước sẽ không được sử dụng lại. Có thể xóa toàn bộ video từ các quest trước đó.</t>
+          <t>Tài nguyên cốt truyện cũ sẽ không được sử dụng lại. Toàn bộ video từ nhiệm vụ trước có thể xóa bỏ.</t>
         </is>
       </c>
     </row>
@@ -9167,8 +9167,8 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Dựa trên tiến độ câu chuyện, vị trí và các yếu tố khác của Rover, các tài nguyên môi trường cần thiết cho trạng thái hiện tại của Rover sẽ được giữ lại. Tất cả các tài nguyên môi trường không thiết yếu khác có thể được xóa.
-Sau khi tài nguyên môi trường được xóa, bạn vẫn có thể tải lại chúng trong game thông qua Terminal - Settings - Tải tài nguyên.</t>
+          <t>Dựa trên tiến trình câu chuyện, vị trí và các yếu tố khác của Vận Mệnh Giả, các tài nguyên môi trường cần thiết cho trạng thái hiện tại của Vận Mệnh Giả sẽ được giữ lại. Tất cả tài nguyên môi trường không cần thiết khác có thể bị xóa.
+Sau khi xóa tài nguyên môi trường, bạn vẫn có thể tải lại trong trò chơi qua Thiết bị đầu cuối - Cài đặt - Tải tài nguyên.</t>
         </is>
       </c>
     </row>
@@ -9298,7 +9298,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Cho phép tự động dọn dẹp tài nguyên quest trước đó</t>
+          <t>Cho phép tự động dọn dẹp tài nguyên nhiệm vụ trước đó</t>
         </is>
       </c>
     </row>
@@ -9363,7 +9363,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Clear Resources ({0}/{1})</t>
+          <t>Thanh Tẩy Tài Nguyên ({0}/{1})</t>
         </is>
       </c>
     </row>
@@ -9428,7 +9428,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Gói Cốt Core</t>
+          <t>Gói Lõi</t>
         </is>
       </c>
     </row>
@@ -9493,7 +9493,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Rover Appearance Switch assets</t>
+          <t>Tài Nguyên Chuyển Đổi Ngoại Hình Rover</t>
         </is>
       </c>
     </row>
@@ -9558,7 +9558,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>[Storyline] Regional storyline assets</t>
+          <t>Tài Nguyên Cốt Truyện Khu Vực</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>[Environment] Jinzhou and other areas</t>
+          <t>[Môi trường] Khu vực Jinzhou và các vùng lân cận</t>
         </is>
       </c>
     </row>
@@ -9688,7 +9688,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>[Environment] Tethys' Deep</t>
+          <t>Tổ Tacet Tethys' Deep</t>
         </is>
       </c>
     </row>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>[Storyline] Tài nguyên cốt truyện tại Ragunna và các khu vực khác</t>
+          <t>Tài Nguyên Cốt Truyện tại Ragunna và Các Khu Vực Khác</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>[Environment] Ragunna and other areas</t>
+          <t>[Môi trường] Khu vực Ragunna và các vùng lân cận</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>[Environment] Septimont and other areas</t>
+          <t>[Môi trường] Khu vực Septimont và các vùng lân cận</t>
         </is>
       </c>
     </row>
@@ -9948,7 +9948,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>[Storyline] Tài nguyên cốt truyện tại Septimont và các khu vực khác</t>
+          <t>Tài Nguyên Cốt Truyện tại Septimont và Các Khu Vực Khác</t>
         </is>
       </c>
     </row>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>[Cốt Truyện] [Storyline] Lahai-Roi Storyline Assets</t>
+          <t>Tài Nguyên Cốt Truyện Lahai-Roi</t>
         </is>
       </c>
     </row>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>[Khu Vực] [Region] Lahai-Roi</t>
+          <t>Lahai-Roi</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>[Cốt Truyện] Tài nguyên cốt truyện tại Roya Frostlands và các khu vực khác</t>
+          <t>Tài Nguyên Cốt Truyện tại Vùng Đất Băng Giá Roya và Các Khu Vực Khác</t>
         </is>
       </c>
     </row>
@@ -10208,7 +10208,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>[Region] Roya Frostlands</t>
+          <t>Vùng Đất Băng Giá Roya</t>
         </is>
       </c>
     </row>
@@ -10273,7 +10273,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>[Cốt truyện] Tài nguyên cốt truyện tại Dimmr Plains và các khu vực khác</t>
+          <t>Tài Nguyên Cốt Truyện tại Đồng Bằng Dimmr và Các Khu Vực Khác</t>
         </is>
       </c>
     </row>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>[Region] Dimmr Plains</t>
+          <t>Đồng Bằng Dimmr</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Huanglong and other areas</t>
+          <t>Huanglong và các khu vực khác</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Rinascita and other areas</t>
+          <t>Khu vực Rinascita và các vùng khác</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Roya Frostlands and other areas</t>
+          <t>Vùng Đất Băng Giá Roya và các khu vực khác</t>
         </is>
       </c>
     </row>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Dọn Dẹp Resources ({0})</t>
+          <t>Thanh Tẩy Tài Nguyên ({0})</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Sau khi xóa tài nguyên môi trường, bạn có thể tải lại chúng trong game. Tiếp tục?</t>
+          <t>Sau khi xóa tài nguyên môi trường, bạn có thể tải lại chúng trong trò chơi. Tiếp tục?</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Không resources to clean</t>
+          <t>Không có tài nguyên để dọn dẹp</t>
         </is>
       </c>
     </row>
@@ -10793,7 +10793,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Không resources to clean</t>
+          <t>Không có tài nguyên để dọn dẹp</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Previous Quest Resources</t>
+          <t>Tài Nguyên Nhiệm Vụ Trước</t>
         </is>
       </c>
     </row>
